--- a/public/templates/office/Subcontract_외주_검수확인서_및_기성평가표.xlsx
+++ b/public/templates/office/Subcontract_외주_검수확인서_및_기성평가표.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외주_검수평가표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_외주산출물_정량검수표" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,12 +30,13 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001E293B"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="0064748B"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -44,11 +47,17 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00334155"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001E293B"/>
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,14 +66,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,28 +116,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,268 +525,308 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>외주_검수평가표</t>
+          <t>[EMP-XLS-S5] 외주 개발 산출물 검수확인서 및 정량 기성 평가표 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>엠파시 사업 및 개발 방법론 표준 시트 (주식회사 엠파시)</t>
+          <t>하수급 협력사 ㈜데이터브릿지(기간계 연계 어댑터 및 일배치 모듈) 최종 납품 검수 및 잔금 지급 승인서 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>과업 번호</t>
+          <t>과업 코드</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>모듈/과업 명칭</t>
+          <t>외주 개발 모듈 및 산출물 명칭</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>배정 M/D</t>
+          <t>배점(가중치)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>목표 기능 수</t>
+          <t>정량 검수 기준 (Acceptance Criteria)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>완료 기능 수</t>
+          <t>실측 결과</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>진척률 (%)</t>
+          <t>득점</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>코드 품질 점검</t>
+          <t>합격 판정</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>단위테스트 통과율</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>검수 판정 (적격/보완)</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대금 지급 승인액</t>
+          <t>검수관 확인</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
+    <row r="5" ht="21" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>MOD-01</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>회원 SSO 연계 모듈</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
+          <t>SUB-IF-01</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>HB-SSO OAuth 2.0 / OIDC 통합인증 어댑터</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>로그인·토큰검증 응답 100ms 이내, 권한 매핑 오류 0건</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>평균 42ms / 오류 0건</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>합격 (Pass)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>강동현 수석</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>SUB-IF-02</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>MarketingHub 심의 요청·결과 Webhook API 2종</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>동시 100 VU 송수신 성공률 99.9%+, 재시도 큐 정상 동작</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>성공률 100.0% 확인</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>합격 (Pass)</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>김태호 책임</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SUB-IF-03</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ProductLab 전성분 마스터 02:00 일배치 동기화 잡</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>10만 건 Delta Upsert 5분 이내 완료 및 정합성 100%</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>3분 12초 / 정합성 100%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>합격 (Pass)</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>조현우 선임</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>SUB-DOC-01</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>연계설계서(EMP_DEG_120)·배치설계서·단위시험서 납품</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="4">
-        <f>E5/D5*100</f>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>전사 표준 양식 준수 및 JUnit 커버리지 85% 이상</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>커버리지 89.4% 달성</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>합격 (Pass)</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>박진우 수석</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SUB-SEC-01</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>시큐어코딩 49개 약점 진단 및 Lombok·URL 표준 준수</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>보안 약점 0건, /api/v1/... 단일 URL 100% 준수</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>위반 0건 (Clean)</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>합격 (Pass)</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>오승민 수석</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>주식회사 데이터브릿지 도급 과업 최종 검수 종합</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>합격 기준: 90점 이상 및 치명 결함 0건</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>100점 만점 달성</t>
+        </is>
+      </c>
+      <c r="F10" s="13">
+        <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Lombok/표준 준수 (양호)</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>100.0 % (15/15건)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>적격</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>MOD-02</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>세금계산서 연계 API</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6">
-        <f>E6/D6*100</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>암호화 처리 완료 (양호)</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>100.0 % (20/20건)</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>적격</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>6750000</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>MOD-03</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>일일 배치 스케줄러</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="4">
-        <f>E7/D7*100</f>
-        <v/>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>비관적 락 적용 (양호)</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>100.0 % (10/10건)</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>적격</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>총 3개 외주 모듈 전체</t>
-        </is>
-      </c>
-      <c r="C8" s="6">
-        <f>SUM(C5:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="6">
-        <f>SUM(D5:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>SUM(E5:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="6">
-        <f>E8/D8*100</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>전 항목 품질 통과</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>100.0 % 통과</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>최종 합격</t>
         </is>
       </c>
-      <c r="J8" s="6">
-        <f>SUM(J5:J7)</f>
-        <v/>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>잔금 ₩18,000,000 지급 승인</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/templates/office/Subcontract_외주_검수확인서_및_기성평가표.xlsx
+++ b/public/templates/office/Subcontract_외주_검수확인서_및_기성평가표.xlsx
@@ -541,7 +541,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[EMP-XLS-S5] 외주 개발 산출물 검수확인서 및 정량 기성 평가표 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[EMP-XLS-S5] 외주 개발 산출물 검수확인서 및 정량 기성 평가표 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>MarketingHub 심의 요청·결과 Webhook API 2종</t>
+          <t>SRM-Portal 검증 요청·결과 Webhook API 2종</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>ProductLab 전성분 마스터 02:00 일배치 동기화 잡</t>
+          <t>PLM-Nexus 자재BOM 마스터 02:00 일배치 동기화 잡</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
